--- a/artfynd/A 16776-2026 artfynd.xlsx
+++ b/artfynd/A 16776-2026 artfynd.xlsx
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133215279</v>
+        <v>133214819</v>
       </c>
       <c r="B3" t="n">
-        <v>58332</v>
+        <v>58641</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -797,16 +797,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103015</v>
+        <v>103044</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -817,17 +817,17 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Fisklösan, Fisklösan, Sm</t>
+          <t>Fisklösan, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>576423</v>
+        <v>576456</v>
       </c>
       <c r="R3" t="n">
-        <v>6316219</v>
+        <v>6316182</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -883,10 +883,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133214819</v>
+        <v>133215279</v>
       </c>
       <c r="B4" t="n">
-        <v>58641</v>
+        <v>58332</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -894,16 +894,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103044</v>
+        <v>103015</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -914,17 +914,17 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Fisklösan, Sm</t>
+          <t>Fisklösan, Fisklösan, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>576456</v>
+        <v>576423</v>
       </c>
       <c r="R4" t="n">
-        <v>6316182</v>
+        <v>6316219</v>
       </c>
       <c r="S4" t="n">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>

--- a/artfynd/A 16776-2026 artfynd.xlsx
+++ b/artfynd/A 16776-2026 artfynd.xlsx
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133214819</v>
+        <v>133215279</v>
       </c>
       <c r="B3" t="n">
-        <v>58641</v>
+        <v>58332</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -797,16 +797,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103044</v>
+        <v>103015</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -817,17 +817,17 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Fisklösan, Sm</t>
+          <t>Fisklösan, Fisklösan, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>576456</v>
+        <v>576423</v>
       </c>
       <c r="R3" t="n">
-        <v>6316182</v>
+        <v>6316219</v>
       </c>
       <c r="S3" t="n">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -883,10 +883,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133215279</v>
+        <v>133214819</v>
       </c>
       <c r="B4" t="n">
-        <v>58332</v>
+        <v>58641</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -894,16 +894,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103015</v>
+        <v>103044</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -914,17 +914,17 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Fisklösan, Fisklösan, Sm</t>
+          <t>Fisklösan, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>576423</v>
+        <v>576456</v>
       </c>
       <c r="R4" t="n">
-        <v>6316219</v>
+        <v>6316182</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>

--- a/artfynd/A 16776-2026 artfynd.xlsx
+++ b/artfynd/A 16776-2026 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>74602177</v>
+        <v>133214932</v>
       </c>
       <c r="B2" t="n">
-        <v>97540</v>
+        <v>57972</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,37 +686,42 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>23 V Fisklösan, Sm</t>
+          <t>Fisklösan, Fisklösan, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>576475</v>
+        <v>576456</v>
       </c>
       <c r="R2" t="n">
-        <v>6316168</v>
+        <v>6316182</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -740,17 +745,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>1986-01-01</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1989-12-31</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Smålands flora 2007: KOO: 5G3f 2425. SOM: Lycopodium annotinum. LEG: Ulf Arup</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -761,28 +761,19 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>Fuktig skog vid sjö</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Margareta Edqvist</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Via Margareta Edqvist</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>Smålands flora (1978-2007)</t>
-        </is>
-      </c>
+          <t>Lars Engström</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -980,53 +971,48 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>133214932</v>
+        <v>74602177</v>
       </c>
       <c r="B5" t="n">
-        <v>57972</v>
+        <v>97983</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Fisklösan, Fisklösan, Sm</t>
+          <t>23 V Fisklösan, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>576456</v>
+        <v>576475</v>
       </c>
       <c r="R5" t="n">
-        <v>6316182</v>
+        <v>6316168</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1050,12 +1036,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>1986-01-01</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>1989-12-31</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Smålands flora 2007: KOO: 5G3f 2425. SOM: Lycopodium annotinum. LEG: Ulf Arup</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1066,19 +1057,28 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Fuktig skog vid sjö</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Margareta Edqvist</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr"/>
+          <t>Via Margareta Edqvist</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Smålands flora (1978-2007)</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
